--- a/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/ISMS-IMP-A.8.17.2_Time_Synchronisation_Status_Assessment_20260301.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/ISMS-IMP-A.8.17.2_Time_Synchronisation_Status_Assessment_20260301.xlsx
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>01.03.2026 11:19:55</t>
+          <t>01.03.2026 17:58:07</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>01.03.2026 11:19:55</t>
+          <t>01.03.2026 17:58:07</t>
         </is>
       </c>
       <c r="K5" s="16" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>01.03.2026 11:19:55</t>
+          <t>01.03.2026 17:58:07</t>
         </is>
       </c>
       <c r="K6" s="16" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>01.03.2026 11:19:55</t>
+          <t>01.03.2026 17:58:07</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
